--- a/sektorler/Elektrik Enerji Ürt.Teçh_Tesis Kurulum.xlsx
+++ b/sektorler/Elektrik Enerji Ürt.Teçh_Tesis Kurulum.xlsx
@@ -553,379 +553,389 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SMRTG</t>
+          <t>ORGE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4633827218</v>
+        <v>4540468594</v>
       </c>
       <c r="C2" t="n">
-        <v>605880000</v>
+        <v>80000000</v>
       </c>
       <c r="D2" t="n">
-        <v>9258174366</v>
+        <v>-187930093</v>
       </c>
       <c r="E2" t="n">
-        <v>7.630000114440918</v>
+        <v>101.9000015258789</v>
       </c>
       <c r="F2" t="n">
-        <v>4622864469.337463</v>
+        <v>8152000122.070312</v>
       </c>
       <c r="G2" t="n">
-        <v>13881038835.33746</v>
+        <v>7964070029.070312</v>
       </c>
       <c r="H2" t="n">
-        <v>10581001663</v>
+        <v>4079111683</v>
       </c>
       <c r="I2" t="n">
-        <v>1562727429</v>
+        <v>2223507120</v>
       </c>
       <c r="J2" t="n">
-        <v>2204071600</v>
+        <v>2237632681</v>
       </c>
       <c r="K2" t="n">
-        <v>-434718338</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>808915635</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10.07768890765761</v>
+      </c>
       <c r="M2" t="n">
-        <v>6.297907397989005</v>
+        <v>3.55914985363512</v>
       </c>
       <c r="N2" t="n">
-        <v>1.31188324862259</v>
+        <v>1.952403034773763</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9976341913181501</v>
+        <v>1.795409428190467</v>
       </c>
       <c r="P2" t="n">
-        <v>33.80430984653041</v>
+        <v>27.27560214308865</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>245118340060.9239</v>
+      </c>
       <c r="S2" t="n">
-        <v>37820449053.77374</v>
+        <v>43708468722.73949</v>
       </c>
       <c r="T2" t="n">
-        <v>41818867039.21317</v>
+        <v>19784126583.75822</v>
       </c>
       <c r="U2" t="n">
-        <v>15722010739.74245</v>
+        <v>15169476238.15556</v>
       </c>
       <c r="V2" t="n">
-        <v>31787108944.24312</v>
+        <v>80945102901.39429</v>
       </c>
       <c r="W2" t="n">
-        <v>52.46436413851442</v>
+        <v>1011.813786267429</v>
       </c>
       <c r="X2" t="n">
-        <v>-85.45679483640271</v>
+        <v>-89.92897676342334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ORGE</t>
+          <t>GESAN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3964498892</v>
+        <v>15338755000</v>
       </c>
       <c r="C3" t="n">
-        <v>80000000</v>
+        <v>460000000</v>
       </c>
       <c r="D3" t="n">
-        <v>-203797179</v>
+        <v>4578427000</v>
       </c>
       <c r="E3" t="n">
-        <v>85.5</v>
+        <v>78.25</v>
       </c>
       <c r="F3" t="n">
-        <v>6840000000</v>
+        <v>35995000000</v>
       </c>
       <c r="G3" t="n">
-        <v>6636202821</v>
+        <v>40573427000</v>
       </c>
       <c r="H3" t="n">
-        <v>3495512127</v>
+        <v>24301047474</v>
       </c>
       <c r="I3" t="n">
-        <v>1713482585</v>
+        <v>4733063493</v>
       </c>
       <c r="J3" t="n">
-        <v>1726412645</v>
+        <v>5314027605</v>
       </c>
       <c r="K3" t="n">
-        <v>593290550</v>
+        <v>635786287</v>
       </c>
       <c r="L3" t="n">
-        <v>11.52892120058208</v>
+        <v>56.61493608150123</v>
       </c>
       <c r="M3" t="n">
-        <v>3.843926213248977</v>
+        <v>7.635155482034798</v>
       </c>
       <c r="N3" t="n">
-        <v>1.898492289510515</v>
+        <v>1.669616383549311</v>
       </c>
       <c r="O3" t="n">
-        <v>1.725312627480487</v>
+        <v>2.346670248009046</v>
       </c>
       <c r="P3" t="n">
-        <v>25.05091498538012</v>
+        <v>13.14922487289901</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>192656530001.3495</v>
+      </c>
       <c r="S3" t="n">
-        <v>37079700294.43896</v>
+        <v>98776044726.58833</v>
       </c>
       <c r="T3" t="n">
-        <v>17077475430.79821</v>
+        <v>112164662731.1246</v>
       </c>
       <c r="U3" t="n">
-        <v>13451061342.03751</v>
+        <v>51246005710.26212</v>
       </c>
       <c r="V3" t="n">
-        <v>22536079022.42489</v>
+        <v>113710810792.3311</v>
       </c>
       <c r="W3" t="n">
-        <v>281.7009877803112</v>
+        <v>247.1974147659373</v>
       </c>
       <c r="X3" t="n">
-        <v>-69.64866872718298</v>
+        <v>-68.34513820701069</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GESAN</t>
+          <t>SAYAS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13639026000</v>
+        <v>1374469210</v>
       </c>
       <c r="C4" t="n">
-        <v>460000000</v>
+        <v>77250000</v>
       </c>
       <c r="D4" t="n">
-        <v>3251319000</v>
+        <v>77579204</v>
       </c>
       <c r="E4" t="n">
-        <v>49.79999923706055</v>
+        <v>49.52000045776367</v>
       </c>
       <c r="F4" t="n">
-        <v>22907999649.04785</v>
+        <v>3825420035.362244</v>
       </c>
       <c r="G4" t="n">
-        <v>26159318649.04785</v>
+        <v>3902999239.362244</v>
       </c>
       <c r="H4" t="n">
-        <v>20597209000</v>
+        <v>2515377738</v>
       </c>
       <c r="I4" t="n">
-        <v>3241086000</v>
+        <v>444238262</v>
       </c>
       <c r="J4" t="n">
-        <v>3749973000</v>
+        <v>494333891</v>
       </c>
       <c r="K4" t="n">
-        <v>903414000</v>
+        <v>258119351</v>
       </c>
       <c r="L4" t="n">
-        <v>25.3571448406244</v>
+        <v>14.82035353235583</v>
       </c>
       <c r="M4" t="n">
-        <v>6.975868532666196</v>
+        <v>7.895471685072557</v>
       </c>
       <c r="N4" t="n">
-        <v>1.270041909515403</v>
+        <v>1.551655316177504</v>
       </c>
       <c r="O4" t="n">
-        <v>1.679592050711528</v>
+        <v>2.783198057497588</v>
       </c>
       <c r="P4" t="n">
-        <v>14.14827156300708</v>
+        <v>11.61279697114185</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>78215556872.90303</v>
+      </c>
       <c r="S4" t="n">
-        <v>76847515675.47932</v>
+        <v>9536901931.322197</v>
       </c>
       <c r="T4" t="n">
-        <v>96176365677.87448</v>
+        <v>12006384225.52666</v>
       </c>
       <c r="U4" t="n">
-        <v>46275552186.8978</v>
+        <v>4592032207.583958</v>
       </c>
       <c r="V4" t="n">
-        <v>73099811180.08388</v>
+        <v>26087718809.33396</v>
       </c>
       <c r="W4" t="n">
-        <v>158.9126330001824</v>
+        <v>337.7050978554558</v>
       </c>
       <c r="X4" t="n">
-        <v>-68.66202623613731</v>
+        <v>-85.33631835224496</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SAYAS</t>
+          <t>CWENE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1231481752</v>
+        <v>17726875532</v>
       </c>
       <c r="C5" t="n">
-        <v>77250000</v>
+        <v>1078290009</v>
       </c>
       <c r="D5" t="n">
-        <v>62203180</v>
+        <v>9426161231</v>
       </c>
       <c r="E5" t="n">
-        <v>48.7400016784668</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="F5" t="n">
-        <v>3765165129.66156</v>
+        <v>39573244152.96999</v>
       </c>
       <c r="G5" t="n">
-        <v>3827368309.66156</v>
+        <v>48999405383.96999</v>
       </c>
       <c r="H5" t="n">
-        <v>2021511533</v>
+        <v>20718524175</v>
       </c>
       <c r="I5" t="n">
-        <v>315737517</v>
+        <v>3622459536</v>
       </c>
       <c r="J5" t="n">
-        <v>363376030</v>
+        <v>4637150750</v>
       </c>
       <c r="K5" t="n">
-        <v>153872941</v>
+        <v>3217725561</v>
       </c>
       <c r="L5" t="n">
-        <v>24.46931283169248</v>
+        <v>12.29851440179115</v>
       </c>
       <c r="M5" t="n">
-        <v>10.53280346989745</v>
+        <v>10.56670529504998</v>
       </c>
       <c r="N5" t="n">
-        <v>1.893320046500848</v>
+        <v>2.365004619542115</v>
       </c>
       <c r="O5" t="n">
-        <v>3.057426651711815</v>
+        <v>2.232386868263029</v>
       </c>
       <c r="P5" t="n">
-        <v>8.38575483748785</v>
+        <v>9.153809887300163</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>975038080805.4539</v>
+      </c>
       <c r="S5" t="n">
-        <v>7699451784.449615</v>
+        <v>80763484308.63826</v>
       </c>
       <c r="T5" t="n">
-        <v>9696119477.978109</v>
+        <v>90106360132.38342</v>
       </c>
       <c r="U5" t="n">
-        <v>4178267427.73922</v>
+        <v>59224595786.16243</v>
       </c>
       <c r="V5" t="n">
-        <v>7191279563.388982</v>
+        <v>301283130258.1595</v>
       </c>
       <c r="W5" t="n">
-        <v>93.09099758432339</v>
+        <v>279.4082554261703</v>
       </c>
       <c r="X5" t="n">
-        <v>-47.64262609355187</v>
+        <v>-86.86509791668023</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>SMRTG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16106307516</v>
+        <v>5062845915</v>
       </c>
       <c r="C6" t="n">
-        <v>1078290009</v>
+        <v>1817640000</v>
       </c>
       <c r="D6" t="n">
-        <v>8070085543</v>
+        <v>10536161983</v>
       </c>
       <c r="E6" t="n">
-        <v>36.63999938964844</v>
+        <v>10.98999977111816</v>
       </c>
       <c r="F6" t="n">
-        <v>39508545271.62401</v>
+        <v>19975863183.97522</v>
       </c>
       <c r="G6" t="n">
-        <v>47578630814.62401</v>
+        <v>30512025166.97522</v>
       </c>
       <c r="H6" t="n">
-        <v>19028876757</v>
+        <v>10784325417</v>
       </c>
       <c r="I6" t="n">
-        <v>2922358194</v>
+        <v>1536662874</v>
       </c>
       <c r="J6" t="n">
-        <v>3785112179</v>
+        <v>2298280342</v>
       </c>
       <c r="K6" t="n">
-        <v>2804131091</v>
-      </c>
-      <c r="L6" t="n">
-        <v>14.0894073741519</v>
-      </c>
+        <v>-51708552</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>12.56993942705126</v>
+        <v>13.27602408173721</v>
       </c>
       <c r="N6" t="n">
-        <v>2.500338376363788</v>
+        <v>2.829293811820369</v>
       </c>
       <c r="O6" t="n">
-        <v>2.452985902099301</v>
+        <v>3.94557992073026</v>
       </c>
       <c r="P6" t="n">
-        <v>7.396774986040572</v>
+        <v>7.692598111268214</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>-15668771729.44489</v>
+      </c>
       <c r="S6" t="n">
-        <v>72779316480.39172</v>
+        <v>34163935247.11455</v>
       </c>
       <c r="T6" t="n">
-        <v>83786881969.88637</v>
+        <v>41272117935.53003</v>
       </c>
       <c r="U6" t="n">
-        <v>54646737530.58923</v>
+        <v>16914712482.87539</v>
       </c>
       <c r="V6" t="n">
-        <v>70404311993.62244</v>
+        <v>19170498484.01877</v>
       </c>
       <c r="W6" t="n">
-        <v>65.29255710985859</v>
+        <v>10.54691714752028</v>
       </c>
       <c r="X6" t="n">
-        <v>-43.88334442469534</v>
+        <v>4.201062902082775</v>
       </c>
     </row>
     <row r="7">
@@ -935,371 +945,381 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10543794000</v>
+        <v>12170740000</v>
       </c>
       <c r="C7" t="n">
         <v>660000000</v>
       </c>
       <c r="D7" t="n">
-        <v>2322625000</v>
+        <v>2509512000</v>
       </c>
       <c r="E7" t="n">
-        <v>52.40000152587891</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="F7" t="n">
-        <v>34584001007.08008</v>
+        <v>61511997985.83984</v>
       </c>
       <c r="G7" t="n">
-        <v>36906626007.08008</v>
+        <v>64021509985.83984</v>
       </c>
       <c r="H7" t="n">
-        <v>12999679000</v>
+        <v>16294911666</v>
       </c>
       <c r="I7" t="n">
-        <v>1985628000</v>
+        <v>3500837395</v>
       </c>
       <c r="J7" t="n">
-        <v>2368387000</v>
+        <v>3942818043</v>
       </c>
       <c r="K7" t="n">
-        <v>600390000</v>
+        <v>852293167</v>
       </c>
       <c r="L7" t="n">
-        <v>57.6025600144574</v>
+        <v>72.17234675523315</v>
       </c>
       <c r="M7" t="n">
-        <v>15.58302169665687</v>
+        <v>16.23750051045403</v>
       </c>
       <c r="N7" t="n">
-        <v>2.839041333796017</v>
+        <v>3.928926483193115</v>
       </c>
       <c r="O7" t="n">
-        <v>3.280033829101752</v>
+        <v>5.054088575209054</v>
       </c>
       <c r="P7" t="n">
-        <v>5.741464093739472</v>
+        <v>5.691308215684846</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>258262638649.9598</v>
+      </c>
       <c r="S7" t="n">
-        <v>48265749572.44478</v>
+        <v>74175802085.47807</v>
       </c>
       <c r="T7" t="n">
-        <v>60429953979.29698</v>
+        <v>75771818745.92369</v>
       </c>
       <c r="U7" t="n">
-        <v>35773807418.13235</v>
+        <v>40661827608.44121</v>
       </c>
       <c r="V7" t="n">
-        <v>48156503656.6247</v>
+        <v>112218021772.4507</v>
       </c>
       <c r="W7" t="n">
-        <v>72.9643994797344</v>
+        <v>170.0273057158344</v>
       </c>
       <c r="X7" t="n">
-        <v>-28.18415295745315</v>
+        <v>-45.18527682606064</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KLYPV</t>
+          <t>ULUSE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13296169656</v>
+        <v>979739005</v>
       </c>
       <c r="C8" t="n">
-        <v>411441018</v>
+        <v>80000000</v>
       </c>
       <c r="D8" t="n">
-        <v>14071776997</v>
+        <v>1406967636</v>
       </c>
       <c r="E8" t="n">
-        <v>58.95000076293945</v>
+        <v>267.5</v>
       </c>
       <c r="F8" t="n">
-        <v>24254448325.00459</v>
+        <v>21400000000</v>
       </c>
       <c r="G8" t="n">
-        <v>38326225322.00459</v>
+        <v>22806967636</v>
       </c>
       <c r="H8" t="n">
-        <v>8121300519</v>
+        <v>9262878232</v>
       </c>
       <c r="I8" t="n">
-        <v>1267193296</v>
+        <v>1043425265</v>
       </c>
       <c r="J8" t="n">
-        <v>2165349316</v>
+        <v>1287351375</v>
       </c>
       <c r="K8" t="n">
-        <v>-691390420</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>849543961</v>
+      </c>
+      <c r="L8" t="n">
+        <v>25.18998543031254</v>
+      </c>
       <c r="M8" t="n">
-        <v>17.6997886848131</v>
+        <v>17.71619472267236</v>
       </c>
       <c r="N8" t="n">
-        <v>4.719222645725195</v>
+        <v>2.462190159988276</v>
       </c>
       <c r="O8" t="n">
-        <v>1.824168083930817</v>
+        <v>21.84255183348549</v>
       </c>
       <c r="P8" t="n">
-        <v>5.224580988278406</v>
+        <v>4.875818995327102</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>257429571786.0642</v>
+      </c>
       <c r="S8" t="n">
-        <v>32179744514.47388</v>
+        <v>23631201372.46192</v>
       </c>
       <c r="T8" t="n">
-        <v>25131695045.12912</v>
+        <v>43092226308.78103</v>
       </c>
       <c r="U8" t="n">
-        <v>45112282416.79978</v>
+        <v>3273258530.0956</v>
       </c>
       <c r="V8" t="n">
-        <v>34141240658.80093</v>
+        <v>81856564499.35069</v>
       </c>
       <c r="W8" t="n">
-        <v>82.97967184886006</v>
+        <v>1023.207056241884</v>
       </c>
       <c r="X8" t="n">
-        <v>-28.95850339067196</v>
+        <v>-73.85670882856347</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>KLYPV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33280133403</v>
+        <v>16201756742</v>
       </c>
       <c r="C9" t="n">
-        <v>998000000</v>
+        <v>411441018</v>
       </c>
       <c r="D9" t="n">
-        <v>-7924744700</v>
+        <v>13556736177</v>
       </c>
       <c r="E9" t="n">
-        <v>284</v>
+        <v>58.95000076293945</v>
       </c>
       <c r="F9" t="n">
-        <v>283432000000</v>
+        <v>24254448325.00459</v>
       </c>
       <c r="G9" t="n">
-        <v>275507255300</v>
+        <v>37811184502.00459</v>
       </c>
       <c r="H9" t="n">
-        <v>35290767390</v>
+        <v>8194787020</v>
       </c>
       <c r="I9" t="n">
-        <v>10044828679</v>
+        <v>982762408</v>
       </c>
       <c r="J9" t="n">
-        <v>11102586376</v>
+        <v>1997138602</v>
       </c>
       <c r="K9" t="n">
-        <v>7668909328</v>
-      </c>
-      <c r="L9" t="n">
-        <v>36.95858014191924</v>
-      </c>
+        <v>-1187537898</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>24.81469145743847</v>
+        <v>18.93267921622427</v>
       </c>
       <c r="N9" t="n">
-        <v>7.806779950556354</v>
+        <v>4.614053349980118</v>
       </c>
       <c r="O9" t="n">
-        <v>8.516552399830536</v>
+        <v>1.49702582943549</v>
       </c>
       <c r="P9" t="n">
-        <v>3.543999505701544</v>
+        <v>4.051885224644928</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>-359848797232.3575</v>
+      </c>
       <c r="S9" t="n">
-        <v>245074247003.4708</v>
+        <v>25286344912.80686</v>
       </c>
       <c r="T9" t="n">
-        <v>178281771814.3598</v>
+        <v>25811309888.78727</v>
       </c>
       <c r="U9" t="n">
-        <v>112915434729.5362</v>
+        <v>54129250940.9538</v>
       </c>
       <c r="V9" t="n">
-        <v>178757151182.4556</v>
-      </c>
-      <c r="W9" t="n">
-        <v>179.1153819463483</v>
-      </c>
-      <c r="X9" t="n">
-        <v>58.55701331394785</v>
-      </c>
+        <v>-63655472872.45239</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ALFAS</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5286209835</v>
+        <v>38403565895</v>
       </c>
       <c r="C10" t="n">
-        <v>368000000</v>
+        <v>998000000</v>
       </c>
       <c r="D10" t="n">
-        <v>2590933667</v>
+        <v>-8564703652</v>
       </c>
       <c r="E10" t="n">
-        <v>41.22000122070312</v>
+        <v>296</v>
       </c>
       <c r="F10" t="n">
-        <v>15168960449.21875</v>
+        <v>295408000000</v>
       </c>
       <c r="G10" t="n">
-        <v>17759894116.21875</v>
+        <v>286843296348</v>
       </c>
       <c r="H10" t="n">
-        <v>8236540064</v>
+        <v>39905134221</v>
       </c>
       <c r="I10" t="n">
-        <v>487176152</v>
+        <v>11709637352</v>
       </c>
       <c r="J10" t="n">
-        <v>703179416</v>
+        <v>12952932020</v>
       </c>
       <c r="K10" t="n">
-        <v>-10754513</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>9063200108</v>
+      </c>
+      <c r="L10" t="n">
+        <v>32.59422681611611</v>
+      </c>
       <c r="M10" t="n">
-        <v>25.25656142957795</v>
+        <v>22.1450476158679</v>
       </c>
       <c r="N10" t="n">
-        <v>2.156232347347294</v>
+        <v>7.188130097731867</v>
       </c>
       <c r="O10" t="n">
-        <v>2.869534302022037</v>
+        <v>7.692202354533463</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2116647256806</v>
+        <v>3.963886337539945</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>2746339012365.543</v>
+      </c>
       <c r="S10" t="n">
-        <v>12428868286.07649</v>
+        <v>260491028795.264</v>
       </c>
       <c r="T10" t="n">
-        <v>37168827391.89259</v>
+        <v>200270376836.6281</v>
       </c>
       <c r="U10" t="n">
-        <v>17935465413.03132</v>
+        <v>128304373930.5829</v>
       </c>
       <c r="V10" t="n">
-        <v>22511053697.00014</v>
+        <v>833851197982.0045</v>
       </c>
       <c r="W10" t="n">
-        <v>61.17134156793516</v>
+        <v>835.5222424669383</v>
       </c>
       <c r="X10" t="n">
-        <v>-32.61550235100638</v>
+        <v>-64.57305563451679</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ULUSE</t>
+          <t>ALFAS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>196772712</v>
+        <v>5872170565</v>
       </c>
       <c r="C11" t="n">
-        <v>80000000</v>
+        <v>368000000</v>
       </c>
       <c r="D11" t="n">
-        <v>1392936072</v>
+        <v>2051080125</v>
       </c>
       <c r="E11" t="n">
-        <v>221.1000061035156</v>
+        <v>38.2599983215332</v>
       </c>
       <c r="F11" t="n">
-        <v>17688000488.28125</v>
+        <v>14079679382.32422</v>
       </c>
       <c r="G11" t="n">
-        <v>19080936560.28125</v>
+        <v>16130759507.32422</v>
       </c>
       <c r="H11" t="n">
-        <v>7213705027</v>
+        <v>7959750160</v>
       </c>
       <c r="I11" t="n">
-        <v>182519227</v>
+        <v>297895265</v>
       </c>
       <c r="J11" t="n">
-        <v>369490978</v>
+        <v>544306132</v>
       </c>
       <c r="K11" t="n">
-        <v>-188081415</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>66454693</v>
+      </c>
+      <c r="L11" t="n">
+        <v>211.8688499896346</v>
+      </c>
       <c r="M11" t="n">
-        <v>51.64114334689182</v>
+        <v>29.63545431328012</v>
       </c>
       <c r="N11" t="n">
-        <v>2.645095202654347</v>
+        <v>2.026540931948575</v>
       </c>
       <c r="O11" t="n">
-        <v>89.89051534890289</v>
+        <v>2.397695916096779</v>
       </c>
       <c r="P11" t="n">
-        <v>1.031881625743529</v>
+        <v>2.115781594955784</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>20137160579.69172</v>
+      </c>
       <c r="S11" t="n">
-        <v>6499333221.913095</v>
+        <v>8535329452.073067</v>
       </c>
       <c r="T11" t="n">
-        <v>33429354112.25526</v>
+        <v>36187840570.10278</v>
       </c>
       <c r="U11" t="n">
-        <v>667625818.9634224</v>
+        <v>19618625260.36977</v>
       </c>
       <c r="V11" t="n">
-        <v>13532104384.37726</v>
+        <v>21119738965.55933</v>
       </c>
       <c r="W11" t="n">
-        <v>169.1513048047157</v>
+        <v>57.39059501510688</v>
       </c>
       <c r="X11" t="n">
-        <v>30.71138077165554</v>
+        <v>-33.33402744567807</v>
       </c>
     </row>
     <row r="12">
@@ -1309,72 +1329,70 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12924292007</v>
+        <v>15218561138</v>
       </c>
       <c r="C12" t="n">
         <v>2950000000</v>
       </c>
       <c r="D12" t="n">
-        <v>4027404292</v>
+        <v>7810827907</v>
       </c>
       <c r="E12" t="n">
-        <v>64.05000305175781</v>
+        <v>36.36000061035156</v>
       </c>
       <c r="F12" t="n">
-        <v>188947509002.6855</v>
+        <v>107262001800.5371</v>
       </c>
       <c r="G12" t="n">
-        <v>192974913294.6855</v>
+        <v>115072829707.5371</v>
       </c>
       <c r="H12" t="n">
-        <v>1375486112</v>
+        <v>1596905643</v>
       </c>
       <c r="I12" t="n">
-        <v>68741193</v>
+        <v>159435480</v>
       </c>
       <c r="J12" t="n">
-        <v>501005803</v>
+        <v>530310986</v>
       </c>
       <c r="K12" t="n">
-        <v>-1615841810</v>
+        <v>-785848622</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>385.1750062357772</v>
+        <v>216.991223537536</v>
       </c>
       <c r="N12" t="n">
-        <v>140.2957918739681</v>
+        <v>72.05988043937116</v>
       </c>
       <c r="O12" t="n">
-        <v>14.61956360165405</v>
+        <v>7.048104011141313</v>
       </c>
       <c r="P12" t="n">
-        <v>0.03638110571705021</v>
+        <v>0.1486411565360154</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>-238128553126.3151</v>
+      </c>
       <c r="S12" t="n">
-        <v>6674001021.038992</v>
+        <v>2503384943.017021</v>
       </c>
       <c r="T12" t="n">
-        <v>2612398189.13866</v>
+        <v>-139236837.8351974</v>
       </c>
       <c r="U12" t="n">
-        <v>43850546897.45695</v>
+        <v>50844444088.18846</v>
       </c>
       <c r="V12" t="n">
-        <v>17712315369.21153</v>
-      </c>
-      <c r="W12" t="n">
-        <v>6.004174701427639</v>
-      </c>
-      <c r="X12" t="n">
-        <v>966.7578182981313</v>
-      </c>
+        <v>-46229990233.23621</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1383,114 +1401,122 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>979835640</v>
+        <v>1050946163</v>
       </c>
       <c r="C13" t="n">
         <v>150000000</v>
       </c>
       <c r="D13" t="n">
-        <v>338910978</v>
+        <v>391401015</v>
       </c>
       <c r="E13" t="n">
-        <v>26.07999992370605</v>
+        <v>267.5</v>
       </c>
       <c r="F13" t="n">
-        <v>3911999988.555908</v>
+        <v>40125000000</v>
       </c>
       <c r="G13" t="n">
-        <v>4250910966.555908</v>
+        <v>40516401015</v>
       </c>
       <c r="H13" t="n">
-        <v>876130843</v>
+        <v>1063566355</v>
       </c>
       <c r="I13" t="n">
-        <v>-34979672</v>
+        <v>23624621</v>
       </c>
       <c r="J13" t="n">
-        <v>-1320487</v>
+        <v>66474435</v>
       </c>
       <c r="K13" t="n">
-        <v>-56667893</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+        <v>45174590</v>
+      </c>
+      <c r="L13" t="n">
+        <v>888.2205682442275</v>
+      </c>
+      <c r="M13" t="n">
+        <v>609.5035033392912</v>
+      </c>
       <c r="N13" t="n">
-        <v>4.851913387731184</v>
+        <v>38.09485024091421</v>
       </c>
       <c r="O13" t="n">
-        <v>3.992506323362465</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
+        <v>38.17988153214277</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.05887756012461059</v>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>13688844713.3709</v>
+      </c>
       <c r="S13" t="n">
-        <v>-367116373.0532763</v>
+        <v>901484649.7797625</v>
       </c>
       <c r="T13" t="n">
-        <v>3890383447.005075</v>
+        <v>4718009291.268271</v>
       </c>
       <c r="U13" t="n">
-        <v>3324462853.388681</v>
+        <v>3511158048.373291</v>
       </c>
       <c r="V13" t="n">
-        <v>2282576642.446826</v>
+        <v>5704874175.698055</v>
       </c>
       <c r="W13" t="n">
-        <v>15.21717761631218</v>
+        <v>38.03249450465371</v>
       </c>
       <c r="X13" t="n">
-        <v>71.38526329448499</v>
+        <v>603.3459242786937</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>MOGAN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5841442148</v>
+        <v>83859863477</v>
       </c>
       <c r="C14" t="n">
-        <v>650000000</v>
+        <v>2440108000</v>
       </c>
       <c r="D14" t="n">
-        <v>14231101204</v>
+        <v>30095211312</v>
       </c>
       <c r="E14" t="n">
-        <v>10.40999984741211</v>
+        <v>38.2599983215332</v>
       </c>
       <c r="F14" t="n">
-        <v>6766499900.817871</v>
+        <v>93358527984.35974</v>
       </c>
       <c r="G14" t="n">
-        <v>20997601104.81787</v>
+        <v>123453739296.3597</v>
       </c>
       <c r="H14" t="n">
-        <v>16893125883</v>
+        <v>14223697789</v>
       </c>
       <c r="I14" t="n">
-        <v>-423194607</v>
+        <v>-2912037216</v>
       </c>
       <c r="J14" t="n">
-        <v>350467789</v>
+        <v>7818850410</v>
       </c>
       <c r="K14" t="n">
-        <v>-730196565</v>
+        <v>-9398172172</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>59.91306979945558</v>
+        <v>15.78924430354459</v>
       </c>
       <c r="N14" t="n">
-        <v>1.242967183826429</v>
+        <v>8.679440545470081</v>
       </c>
       <c r="O14" t="n">
-        <v>1.158361193927872</v>
+        <v>1.113268303971958</v>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
@@ -1498,71 +1524,69 @@
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>-2847842547149.441</v>
+      </c>
       <c r="S14" t="n">
-        <v>-6745164241.202728</v>
+        <v>121976477753.8246</v>
       </c>
       <c r="T14" t="n">
-        <v>67316082859.55754</v>
+        <v>38235934868.6836</v>
       </c>
       <c r="U14" t="n">
-        <v>19819300950.56043</v>
+        <v>280171568201.2095</v>
       </c>
       <c r="V14" t="n">
-        <v>26796739856.30508</v>
-      </c>
-      <c r="W14" t="n">
-        <v>41.22575362508474</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-74.74879430444685</v>
-      </c>
+        <v>-601864641581.4308</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>MOGAN</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>76055301997</v>
+        <v>6516972751</v>
       </c>
       <c r="C15" t="n">
-        <v>2440108000</v>
+        <v>1300000000</v>
       </c>
       <c r="D15" t="n">
-        <v>30020411090</v>
+        <v>13048516194</v>
       </c>
       <c r="E15" t="n">
-        <v>14.5600004196167</v>
+        <v>4.190000057220459</v>
       </c>
       <c r="F15" t="n">
-        <v>35527973503.91006</v>
+        <v>5447000074.386597</v>
       </c>
       <c r="G15" t="n">
-        <v>65548384593.91006</v>
+        <v>18495516268.3866</v>
       </c>
       <c r="H15" t="n">
-        <v>13104902813</v>
+        <v>18665323833</v>
       </c>
       <c r="I15" t="n">
-        <v>-2877939672</v>
+        <v>-432750413</v>
       </c>
       <c r="J15" t="n">
-        <v>6855328521</v>
+        <v>368647286</v>
       </c>
       <c r="K15" t="n">
-        <v>-9168766094</v>
+        <v>-1176043310</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>9.561669348611815</v>
+        <v>50.17130729232223</v>
       </c>
       <c r="N15" t="n">
-        <v>5.001821496065303</v>
+        <v>0.9909025117307</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4671334222735907</v>
+        <v>0.8358175310079022</v>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
@@ -1570,25 +1594,23 @@
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>-356365696883.7727</v>
+      </c>
       <c r="S15" t="n">
-        <v>116408330090.1837</v>
+        <v>-5878559932.929632</v>
       </c>
       <c r="T15" t="n">
-        <v>33240108557.35388</v>
+        <v>76620358262.04182</v>
       </c>
       <c r="U15" t="n">
-        <v>258046366115.3257</v>
+        <v>21772876795.50059</v>
       </c>
       <c r="V15" t="n">
-        <v>135898268254.2878</v>
-      </c>
-      <c r="W15" t="n">
-        <v>55.69354645543877</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-73.85693433750646</v>
-      </c>
+        <v>-65962755439.78999</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1597,44 +1619,44 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6483741793</v>
+        <v>7703042931</v>
       </c>
       <c r="C16" t="n">
         <v>825000000</v>
       </c>
       <c r="D16" t="n">
-        <v>4094068648</v>
+        <v>7871391357</v>
       </c>
       <c r="E16" t="n">
-        <v>7.019999980926514</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="F16" t="n">
-        <v>5791499984.264374</v>
+        <v>4801500141.620636</v>
       </c>
       <c r="G16" t="n">
-        <v>9885568632.264374</v>
+        <v>12672891498.62064</v>
       </c>
       <c r="H16" t="n">
-        <v>1606559809</v>
+        <v>1485997618</v>
       </c>
       <c r="I16" t="n">
-        <v>-262211894</v>
+        <v>-250777415</v>
       </c>
       <c r="J16" t="n">
-        <v>241907650</v>
+        <v>229814453</v>
       </c>
       <c r="K16" t="n">
-        <v>-1114480267</v>
+        <v>-639763427</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>40.86505173467798</v>
+        <v>55.14401436980395</v>
       </c>
       <c r="N16" t="n">
-        <v>6.153252793257431</v>
+        <v>8.528204450069742</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8932342109176854</v>
+        <v>0.6233251177008968</v>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
@@ -1642,25 +1664,23 @@
           <t>Elektrik Enerji Ürt.Teçh/Tesis Kurulum</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>-193861686525.4781</v>
+      </c>
       <c r="S16" t="n">
-        <v>1073040785.610247</v>
+        <v>-3401645779.728039</v>
       </c>
       <c r="T16" t="n">
-        <v>3661182177.750142</v>
+        <v>-732606354.2539301</v>
       </c>
       <c r="U16" t="n">
-        <v>21998545329.28831</v>
+        <v>25735477359.69577</v>
       </c>
       <c r="V16" t="n">
-        <v>8910922764.216234</v>
-      </c>
-      <c r="W16" t="n">
-        <v>10.80111850208028</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-35.00673120497225</v>
-      </c>
+        <v>-43065115324.94107</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1669,45 +1689,47 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>204462834569</v>
+        <v>232020772918</v>
       </c>
       <c r="C17" t="n">
-        <v>11833969027</v>
+        <v>13695729027</v>
       </c>
       <c r="D17" t="n">
-        <v>85603408158</v>
+        <v>94607339396</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>693717467169.4894</v>
+        <v>775169683188.4504</v>
       </c>
       <c r="G17" t="n">
-        <v>779320875327.4894</v>
+        <v>869777022584.4504</v>
       </c>
       <c r="H17" t="n">
-        <v>161442308540</v>
+        <v>181051339024</v>
       </c>
       <c r="I17" t="n">
-        <v>20193152427</v>
+        <v>26681984027</v>
       </c>
       <c r="J17" t="n">
-        <v>36485327816</v>
+        <v>44720069011</v>
       </c>
       <c r="K17" t="n">
-        <v>-1286889405</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
+        <v>2558139372</v>
+      </c>
+      <c r="L17" t="n">
+        <v>303.020895449652</v>
+      </c>
       <c r="M17" t="n">
-        <v>21.35984303766436</v>
+        <v>19.44936673444103</v>
       </c>
       <c r="N17" t="n">
-        <v>4.827240655657496</v>
+        <v>4.804035293376944</v>
       </c>
       <c r="O17" t="n">
-        <v>3.392878068191805</v>
+        <v>3.340949491028582</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0291086117658133</v>
+        <v>0.03442083018165892</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1729,47 +1751,47 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6483741793</v>
+        <v>7703042931</v>
       </c>
       <c r="C18" t="n">
-        <v>605880000</v>
+        <v>660000000</v>
       </c>
       <c r="D18" t="n">
-        <v>3251319000</v>
+        <v>4578427000</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>17688000488.28125</v>
+        <v>24254448325.00459</v>
       </c>
       <c r="G18" t="n">
-        <v>20997601104.81787</v>
+        <v>37811184502.00459</v>
       </c>
       <c r="H18" t="n">
-        <v>8236540064</v>
+        <v>9262878232</v>
       </c>
       <c r="I18" t="n">
-        <v>487176152</v>
+        <v>982762408</v>
       </c>
       <c r="J18" t="n">
-        <v>1726412645</v>
+        <v>1997138602</v>
       </c>
       <c r="K18" t="n">
-        <v>-56667893</v>
+        <v>66454693</v>
       </c>
       <c r="L18" t="n">
-        <v>24.91322883615844</v>
+        <v>32.59422681611611</v>
       </c>
       <c r="M18" t="n">
-        <v>16.64140519073499</v>
+        <v>17.71619472267236</v>
       </c>
       <c r="N18" t="n">
-        <v>2.645095202654347</v>
+        <v>2.829293811820369</v>
       </c>
       <c r="O18" t="n">
-        <v>2.452985902099301</v>
+        <v>2.397695916096779</v>
       </c>
       <c r="P18" t="n">
-        <v>5.741464093739472</v>
+        <v>5.283563605505974</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
